--- a/Excel/liste_groupe_2.xlsx
+++ b/Excel/liste_groupe_2.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\SAPIEN\PowerShell Studio\Files\ASTI\EXCEL\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\SAPIEN\PowerShell Studio\Files\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB6F8910-7E00-48D5-A062-4B6999576041}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4154F4E-0D4D-48C5-9AEE-C353D1EDCD0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Excel/liste_groupe_2.xlsx
+++ b/Excel/liste_groupe_2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\SAPIEN\PowerShell Studio\Files\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4154F4E-0D4D-48C5-9AEE-C353D1EDCD0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E339B957-FB8F-48A0-A5F7-760EC9CC8B4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Excel/liste_groupe_2.xlsx
+++ b/Excel/liste_groupe_2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\SAPIEN\PowerShell Studio\Files\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E339B957-FB8F-48A0-A5F7-760EC9CC8B4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9CF115A-2876-42DF-9272-DF673770647F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Excel/liste_groupe_2.xlsx
+++ b/Excel/liste_groupe_2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\SAPIEN\PowerShell Studio\Files\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9CF115A-2876-42DF-9272-DF673770647F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FCE0042-BCAE-472D-BDCA-145DAA3786D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Excel/liste_groupe_2.xlsx
+++ b/Excel/liste_groupe_2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\SAPIEN\PowerShell Studio\Files\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FCE0042-BCAE-472D-BDCA-145DAA3786D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6E17807-104F-4847-9D9E-ACDDA60EB925}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Excel/liste_groupe_2.xlsx
+++ b/Excel/liste_groupe_2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\SAPIEN\PowerShell Studio\Files\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6E17807-104F-4847-9D9E-ACDDA60EB925}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64A3E4CA-5385-4352-BB9E-4E09AF8302E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Excel/liste_groupe_2.xlsx
+++ b/Excel/liste_groupe_2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\SAPIEN\PowerShell Studio\Files\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64A3E4CA-5385-4352-BB9E-4E09AF8302E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FC08BC1-0D53-4852-BCEA-89B11002C1FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Excel/liste_groupe_2.xlsx
+++ b/Excel/liste_groupe_2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\SAPIEN\PowerShell Studio\Files\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FC08BC1-0D53-4852-BCEA-89B11002C1FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{150E32BE-ABEA-4842-AD80-C9976DF48D82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7995" yWindow="5535" windowWidth="28815" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="84">
   <si>
     <t>Période de présence aux cours 2025 - 2026 (01/11/2025)</t>
   </si>
@@ -275,18 +275,6 @@
   </si>
   <si>
     <t>28/05/2024</t>
-  </si>
-  <si>
-    <t>WRETA</t>
-  </si>
-  <si>
-    <t>Abeje</t>
-  </si>
-  <si>
-    <t>05/05/1997</t>
-  </si>
-  <si>
-    <t>11/09/2025</t>
   </si>
 </sst>
 </file>
@@ -1267,30 +1255,16 @@
       </c>
     </row>
     <row r="21" spans="1:8" ht="39.950000000000003" customHeight="1">
-      <c r="A21" s="5">
+      <c r="A21" s="6">
         <v>18</v>
       </c>
-      <c r="B21" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="C21" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="D21" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F21" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G21" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>15</v>
-      </c>
+      <c r="B21" s="10"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="14"/>
+      <c r="G21" s="14"/>
+      <c r="H21" s="3"/>
     </row>
     <row r="22" spans="1:8" ht="39.950000000000003" customHeight="1">
       <c r="A22" s="6">

--- a/Excel/liste_groupe_2.xlsx
+++ b/Excel/liste_groupe_2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\SAPIEN\PowerShell Studio\Files\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{150E32BE-ABEA-4842-AD80-C9976DF48D82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00574196-AEF3-42C1-A75D-46151ADDC470}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7995" yWindow="5535" windowWidth="28815" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Excel/liste_groupe_2.xlsx
+++ b/Excel/liste_groupe_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\SAPIEN\PowerShell Studio\Files\ASTI\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\AppData\Roaming\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00574196-AEF3-42C1-A75D-46151ADDC470}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39817F75-F6F1-41E4-A1E9-76907E448FC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7995" yWindow="5535" windowWidth="28815" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8685" yWindow="5535" windowWidth="20115" windowHeight="9945" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="92">
   <si>
     <t>Période de présence aux cours 2025 - 2026 (01/11/2025)</t>
   </si>
@@ -52,6 +52,45 @@
     <t>DATE DE FIN</t>
   </si>
   <si>
+    <t>ABAKAR ADAM</t>
+  </si>
+  <si>
+    <t>Seida</t>
+  </si>
+  <si>
+    <t>01/01/1983</t>
+  </si>
+  <si>
+    <t>Soudan</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>10/09/2024</t>
+  </si>
+  <si>
+    <t>01/01/1900</t>
+  </si>
+  <si>
+    <t>ABDRAMAN IBRAHIM</t>
+  </si>
+  <si>
+    <t>Saladin</t>
+  </si>
+  <si>
+    <t>31/12/1899</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>01/09/2025</t>
+  </si>
+  <si>
     <t>ABIA</t>
   </si>
   <si>
@@ -61,18 +100,12 @@
     <t>19/08/2000</t>
   </si>
   <si>
-    <t>RDC</t>
-  </si>
-  <si>
-    <t>F</t>
+    <t>République démocratique du Congo</t>
   </si>
   <si>
     <t>23/09/2025</t>
   </si>
   <si>
-    <t>01/01/1900</t>
-  </si>
-  <si>
     <t>AVAGYAN</t>
   </si>
   <si>
@@ -85,9 +118,6 @@
     <t>Arménie</t>
   </si>
   <si>
-    <t>M</t>
-  </si>
-  <si>
     <t>10/12/2024</t>
   </si>
   <si>
@@ -112,7 +142,7 @@
     <t>Wakgari</t>
   </si>
   <si>
-    <t>Ethiopie</t>
+    <t>Éthiopie</t>
   </si>
   <si>
     <t>16/09/2025</t>
@@ -190,18 +220,6 @@
     <t>15/11/2022</t>
   </si>
   <si>
-    <t>Prénom</t>
-  </si>
-  <si>
-    <t>02/03/1960</t>
-  </si>
-  <si>
-    <t>Andorre</t>
-  </si>
-  <si>
-    <t>02/05/2026</t>
-  </si>
-  <si>
     <t>PETUKHOVA</t>
   </si>
   <si>
@@ -229,9 +247,6 @@
     <t>Algérie</t>
   </si>
   <si>
-    <t>01/09/2025</t>
-  </si>
-  <si>
     <t>SELIMAN</t>
   </si>
   <si>
@@ -241,9 +256,6 @@
     <t>08/07/2004</t>
   </si>
   <si>
-    <t>Soudan</t>
-  </si>
-  <si>
     <t>03/09/2025</t>
   </si>
   <si>
@@ -275,6 +287,18 @@
   </si>
   <si>
     <t>28/05/2024</t>
+  </si>
+  <si>
+    <t>WRETA</t>
+  </si>
+  <si>
+    <t>Abeje</t>
+  </si>
+  <si>
+    <t>05/05/1997</t>
+  </si>
+  <si>
+    <t>11/09/2025</t>
   </si>
 </sst>
 </file>
@@ -369,16 +393,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -390,9 +408,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -402,8 +417,17 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -754,13 +778,13 @@
   <dimension ref="A1:H60"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="3.28515625" style="4" customWidth="1"/>
-    <col min="2" max="2" width="13" style="7" customWidth="1"/>
-    <col min="3" max="3" width="15.42578125" style="7" customWidth="1"/>
-    <col min="4" max="4" width="11.85546875" style="12" customWidth="1"/>
-    <col min="5" max="5" width="11.85546875" customWidth="1"/>
-    <col min="6" max="6" width="9.140625" style="12" customWidth="1"/>
-    <col min="7" max="7" width="15.140625" style="12" customWidth="1"/>
+    <col min="1" max="1" width="3.28515625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="13" style="5" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" style="5" customWidth="1"/>
+    <col min="4" max="4" width="11.85546875" style="9" customWidth="1"/>
+    <col min="5" max="5" width="33" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" style="9" customWidth="1"/>
+    <col min="7" max="7" width="15.140625" style="9" customWidth="1"/>
     <col min="8" max="8" width="12.42578125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -790,13 +814,13 @@
     </row>
     <row r="3" spans="1:8" ht="30" customHeight="1">
       <c r="A3" s="1"/>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="6" t="s">
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
@@ -805,7 +829,7 @@
       <c r="F3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="6" t="s">
         <v>7</v>
       </c>
       <c r="H3" s="1" t="s">
@@ -813,25 +837,25 @@
       </c>
     </row>
     <row r="4" spans="1:8" ht="39.950000000000003" customHeight="1">
-      <c r="A4" s="5">
+      <c r="A4" s="4">
         <v>1</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="D4" s="10" t="s">
         <v>11</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="13" t="s">
+      <c r="F4" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="G4" s="13" t="s">
+      <c r="G4" s="10" t="s">
         <v>14</v>
       </c>
       <c r="H4" s="2" t="s">
@@ -839,25 +863,25 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="39.950000000000003" customHeight="1">
-      <c r="A5" s="5">
+      <c r="A5" s="4">
         <v>2</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="10" t="s">
         <v>18</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="F5" s="13" t="s">
+      <c r="F5" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="G5" s="13" t="s">
+      <c r="G5" s="10" t="s">
         <v>21</v>
       </c>
       <c r="H5" s="2" t="s">
@@ -865,25 +889,25 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="39.950000000000003" customHeight="1">
-      <c r="A6" s="5">
+      <c r="A6" s="4">
         <v>3</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="D6" s="10" t="s">
         <v>24</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="F6" s="13" t="s">
+      <c r="F6" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="G6" s="13" t="s">
+      <c r="G6" s="10" t="s">
         <v>26</v>
       </c>
       <c r="H6" s="2" t="s">
@@ -891,848 +915,876 @@
       </c>
     </row>
     <row r="7" spans="1:8" ht="39.950000000000003" customHeight="1">
-      <c r="A7" s="5">
+      <c r="A7" s="4">
         <v>4</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="13" t="s">
-        <v>15</v>
+      <c r="D7" s="10" t="s">
+        <v>29</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F7" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F7" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="G7" s="13" t="s">
+      <c r="G7" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="39.950000000000003" customHeight="1">
+      <c r="A8" s="4">
+        <v>5</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="39.950000000000003" customHeight="1">
+      <c r="A9" s="4">
+        <v>6</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="39.950000000000003" customHeight="1">
+      <c r="A10" s="4">
+        <v>7</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="39.950000000000003" customHeight="1">
+      <c r="A11" s="4">
+        <v>8</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="H7" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="39.950000000000003" customHeight="1">
-      <c r="A8" s="5">
-        <v>5</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="D8" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="E8" s="2" t="s">
+      <c r="F11" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G11" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="39.950000000000003" customHeight="1">
+      <c r="A12" s="4">
+        <v>9</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G12" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="39.950000000000003" customHeight="1">
+      <c r="A13" s="4">
+        <v>10</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="F8" s="13" t="s">
+      <c r="F13" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G13" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="39.950000000000003" customHeight="1">
+      <c r="A14" s="4">
+        <v>11</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F14" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="G8" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="39.950000000000003" customHeight="1">
-      <c r="A9" s="5">
-        <v>6</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="D9" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F9" s="13" t="s">
+      <c r="G14" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="39.950000000000003" customHeight="1">
+      <c r="A15" s="4">
+        <v>12</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F15" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="G9" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="39.950000000000003" customHeight="1">
-      <c r="A10" s="5">
-        <v>7</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="D10" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F10" s="13" t="s">
+      <c r="G15" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="39.950000000000003" customHeight="1">
+      <c r="A16" s="4">
         <v>13</v>
       </c>
-      <c r="G10" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="39.950000000000003" customHeight="1">
-      <c r="A11" s="5">
-        <v>8</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="D11" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F11" s="13" t="s">
+      <c r="B16" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F16" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="G11" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="39.950000000000003" customHeight="1">
-      <c r="A12" s="5">
-        <v>9</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="D12" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="F12" s="13" t="s">
+      <c r="G16" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="39.950000000000003" customHeight="1">
+      <c r="A17" s="4">
+        <v>14</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="F17" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="G12" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="39.950000000000003" customHeight="1">
-      <c r="A13" s="5">
-        <v>10</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="D13" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F13" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G13" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="39.950000000000003" customHeight="1">
-      <c r="A14" s="5">
-        <v>11</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="D14" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="F14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G14" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="39.950000000000003" customHeight="1">
-      <c r="A15" s="5">
-        <v>12</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F15" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G15" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="39.950000000000003" customHeight="1">
-      <c r="A16" s="5">
-        <v>13</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="F16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G16" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="39.950000000000003" customHeight="1">
-      <c r="A17" s="5">
-        <v>14</v>
-      </c>
-      <c r="B17" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D17" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="F17" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G17" s="13" t="s">
-        <v>73</v>
+      <c r="G17" s="10" t="s">
+        <v>21</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="39.950000000000003" customHeight="1">
-      <c r="A18" s="5">
-        <v>15</v>
-      </c>
-      <c r="B18" s="9" t="s">
+      <c r="A18" s="4">
+        <v>15</v>
+      </c>
+      <c r="B18" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="C18" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="D18" s="13" t="s">
+      <c r="D18" s="10" t="s">
         <v>76</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F18" s="13" t="s">
+      <c r="F18" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G18" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="39.950000000000003" customHeight="1">
+      <c r="A19" s="4">
+        <v>16</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F19" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="G18" s="13" t="s">
+      <c r="G19" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="39.950000000000003" customHeight="1">
+      <c r="A20" s="4">
+        <v>17</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F20" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="G20" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="39.950000000000003" customHeight="1">
+      <c r="A21" s="4">
+        <v>18</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F21" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="G21" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="39.950000000000003" customHeight="1">
+      <c r="A22" s="4">
+        <v>19</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F22" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="G22" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="39.950000000000003" customHeight="1">
+      <c r="A23" s="11">
+        <v>20</v>
+      </c>
+      <c r="B23" s="12"/>
+      <c r="C23" s="12"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="14"/>
+      <c r="F23" s="13"/>
+      <c r="G23" s="13"/>
+      <c r="H23" s="14"/>
+    </row>
+    <row r="24" spans="1:8" ht="39.950000000000003" customHeight="1">
+      <c r="A24" s="11">
+        <v>21</v>
+      </c>
+      <c r="B24" s="12"/>
+      <c r="C24" s="12"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="13"/>
+      <c r="G24" s="13"/>
+      <c r="H24" s="14"/>
+    </row>
+    <row r="25" spans="1:8" ht="39.950000000000003" customHeight="1">
+      <c r="A25" s="11">
+        <v>22</v>
+      </c>
+      <c r="B25" s="12"/>
+      <c r="C25" s="12"/>
+      <c r="D25" s="13"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="13"/>
+      <c r="G25" s="13"/>
+      <c r="H25" s="14"/>
+    </row>
+    <row r="26" spans="1:8" ht="39.950000000000003" customHeight="1">
+      <c r="A26" s="11">
+        <v>23</v>
+      </c>
+      <c r="B26" s="12"/>
+      <c r="C26" s="12"/>
+      <c r="D26" s="13"/>
+      <c r="E26" s="14"/>
+      <c r="F26" s="13"/>
+      <c r="G26" s="13"/>
+      <c r="H26" s="14"/>
+    </row>
+    <row r="27" spans="1:8" ht="39.950000000000003" customHeight="1">
+      <c r="A27" s="11">
+        <v>24</v>
+      </c>
+      <c r="B27" s="12"/>
+      <c r="C27" s="12"/>
+      <c r="D27" s="13"/>
+      <c r="E27" s="14"/>
+      <c r="F27" s="13"/>
+      <c r="G27" s="13"/>
+      <c r="H27" s="14"/>
+    </row>
+    <row r="28" spans="1:8" ht="39.950000000000003" customHeight="1">
+      <c r="A28" s="11">
+        <v>25</v>
+      </c>
+      <c r="B28" s="12"/>
+      <c r="C28" s="12"/>
+      <c r="D28" s="13"/>
+      <c r="E28" s="14"/>
+      <c r="F28" s="13"/>
+      <c r="G28" s="13"/>
+      <c r="H28" s="14"/>
+    </row>
+    <row r="29" spans="1:8" ht="39.950000000000003" customHeight="1">
+      <c r="A29" s="11">
+        <v>26</v>
+      </c>
+      <c r="B29" s="12"/>
+      <c r="C29" s="12"/>
+      <c r="D29" s="13"/>
+      <c r="E29" s="14"/>
+      <c r="F29" s="13"/>
+      <c r="G29" s="13"/>
+      <c r="H29" s="14"/>
+    </row>
+    <row r="30" spans="1:8" ht="39.950000000000003" customHeight="1">
+      <c r="A30" s="11">
+        <v>27</v>
+      </c>
+      <c r="B30" s="12"/>
+      <c r="C30" s="12"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="14"/>
+      <c r="F30" s="13"/>
+      <c r="G30" s="13"/>
+      <c r="H30" s="14"/>
+    </row>
+    <row r="31" spans="1:8" ht="39.950000000000003" customHeight="1">
+      <c r="A31" s="11">
+        <v>28</v>
+      </c>
+      <c r="B31" s="12"/>
+      <c r="C31" s="12"/>
+      <c r="D31" s="13"/>
+      <c r="E31" s="14"/>
+      <c r="F31" s="13"/>
+      <c r="G31" s="13"/>
+      <c r="H31" s="14"/>
+    </row>
+    <row r="32" spans="1:8" ht="39.950000000000003" customHeight="1">
+      <c r="A32" s="11">
+        <v>29</v>
+      </c>
+      <c r="B32" s="12"/>
+      <c r="C32" s="12"/>
+      <c r="D32" s="13"/>
+      <c r="E32" s="14"/>
+      <c r="F32" s="13"/>
+      <c r="G32" s="13"/>
+      <c r="H32" s="14"/>
+    </row>
+    <row r="33" spans="1:8" ht="39.950000000000003" customHeight="1">
+      <c r="A33" s="11">
         <v>30</v>
       </c>
-      <c r="H18" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="39.950000000000003" customHeight="1">
-      <c r="A19" s="5">
-        <v>16</v>
-      </c>
-      <c r="B19" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="C19" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="D19" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F19" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G19" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="39.950000000000003" customHeight="1">
-      <c r="A20" s="5">
-        <v>17</v>
-      </c>
-      <c r="B20" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G20" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="39.950000000000003" customHeight="1">
-      <c r="A21" s="6">
-        <v>18</v>
-      </c>
-      <c r="B21" s="10"/>
-      <c r="C21" s="10"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="3"/>
-    </row>
-    <row r="22" spans="1:8" ht="39.950000000000003" customHeight="1">
-      <c r="A22" s="6">
-        <v>19</v>
-      </c>
-      <c r="B22" s="10"/>
-      <c r="C22" s="10"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="3"/>
-    </row>
-    <row r="23" spans="1:8" ht="39.950000000000003" customHeight="1">
-      <c r="A23" s="6">
-        <v>20</v>
-      </c>
-      <c r="B23" s="10"/>
-      <c r="C23" s="10"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="3"/>
-    </row>
-    <row r="24" spans="1:8" ht="39.950000000000003" customHeight="1">
-      <c r="A24" s="6">
-        <v>21</v>
-      </c>
-      <c r="B24" s="10"/>
-      <c r="C24" s="10"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="3"/>
-    </row>
-    <row r="25" spans="1:8" ht="39.950000000000003" customHeight="1">
-      <c r="A25" s="6">
-        <v>22</v>
-      </c>
-      <c r="B25" s="10"/>
-      <c r="C25" s="10"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="3"/>
-    </row>
-    <row r="26" spans="1:8" ht="39.950000000000003" customHeight="1">
-      <c r="A26" s="6">
-        <v>23</v>
-      </c>
-      <c r="B26" s="10"/>
-      <c r="C26" s="10"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="3"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="3"/>
-    </row>
-    <row r="27" spans="1:8" ht="39.950000000000003" customHeight="1">
-      <c r="A27" s="6">
-        <v>24</v>
-      </c>
-      <c r="B27" s="10"/>
-      <c r="C27" s="10"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="3"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="3"/>
-    </row>
-    <row r="28" spans="1:8" ht="39.950000000000003" customHeight="1">
-      <c r="A28" s="6">
-        <v>25</v>
-      </c>
-      <c r="B28" s="10"/>
-      <c r="C28" s="10"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="3"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="3"/>
-    </row>
-    <row r="29" spans="1:8" ht="39.950000000000003" customHeight="1">
-      <c r="A29" s="6">
-        <v>26</v>
-      </c>
-      <c r="B29" s="10"/>
-      <c r="C29" s="10"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="3"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="3"/>
-    </row>
-    <row r="30" spans="1:8" ht="39.950000000000003" customHeight="1">
-      <c r="A30" s="6">
-        <v>27</v>
-      </c>
-      <c r="B30" s="10"/>
-      <c r="C30" s="10"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="3"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="3"/>
-    </row>
-    <row r="31" spans="1:8" ht="39.950000000000003" customHeight="1">
-      <c r="A31" s="6">
-        <v>28</v>
-      </c>
-      <c r="B31" s="10"/>
-      <c r="C31" s="10"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="3"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="3"/>
-    </row>
-    <row r="32" spans="1:8" ht="39.950000000000003" customHeight="1">
-      <c r="A32" s="6">
-        <v>29</v>
-      </c>
-      <c r="B32" s="10"/>
-      <c r="C32" s="10"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="3"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="3"/>
-    </row>
-    <row r="33" spans="1:8" ht="39.950000000000003" customHeight="1">
-      <c r="A33" s="6">
-        <v>30</v>
-      </c>
-      <c r="B33" s="10"/>
-      <c r="C33" s="10"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="3"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="3"/>
+      <c r="B33" s="12"/>
+      <c r="C33" s="12"/>
+      <c r="D33" s="13"/>
+      <c r="E33" s="14"/>
+      <c r="F33" s="13"/>
+      <c r="G33" s="13"/>
+      <c r="H33" s="14"/>
     </row>
     <row r="34" spans="1:8" ht="39.950000000000003" customHeight="1">
-      <c r="A34" s="6">
+      <c r="A34" s="11">
         <v>31</v>
       </c>
-      <c r="B34" s="10"/>
-      <c r="C34" s="10"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="3"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="3"/>
+      <c r="B34" s="12"/>
+      <c r="C34" s="12"/>
+      <c r="D34" s="13"/>
+      <c r="E34" s="14"/>
+      <c r="F34" s="13"/>
+      <c r="G34" s="13"/>
+      <c r="H34" s="14"/>
     </row>
     <row r="35" spans="1:8" ht="39.950000000000003" customHeight="1">
-      <c r="A35" s="6">
+      <c r="A35" s="11">
         <v>32</v>
       </c>
-      <c r="B35" s="10"/>
-      <c r="C35" s="10"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="3"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="3"/>
+      <c r="B35" s="12"/>
+      <c r="C35" s="12"/>
+      <c r="D35" s="13"/>
+      <c r="E35" s="14"/>
+      <c r="F35" s="13"/>
+      <c r="G35" s="13"/>
+      <c r="H35" s="14"/>
     </row>
     <row r="36" spans="1:8" ht="39.950000000000003" customHeight="1">
-      <c r="A36" s="6">
+      <c r="A36" s="11">
         <v>33</v>
       </c>
-      <c r="B36" s="10"/>
-      <c r="C36" s="10"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="3"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="3"/>
+      <c r="B36" s="12"/>
+      <c r="C36" s="12"/>
+      <c r="D36" s="13"/>
+      <c r="E36" s="14"/>
+      <c r="F36" s="13"/>
+      <c r="G36" s="13"/>
+      <c r="H36" s="14"/>
     </row>
     <row r="37" spans="1:8" ht="39.950000000000003" customHeight="1">
-      <c r="A37" s="6">
+      <c r="A37" s="11">
         <v>34</v>
       </c>
-      <c r="B37" s="10"/>
-      <c r="C37" s="10"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="3"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="3"/>
+      <c r="B37" s="12"/>
+      <c r="C37" s="12"/>
+      <c r="D37" s="13"/>
+      <c r="E37" s="14"/>
+      <c r="F37" s="13"/>
+      <c r="G37" s="13"/>
+      <c r="H37" s="14"/>
     </row>
     <row r="38" spans="1:8" ht="39.950000000000003" customHeight="1">
-      <c r="A38" s="6">
+      <c r="A38" s="11">
         <v>35</v>
       </c>
-      <c r="B38" s="10"/>
-      <c r="C38" s="10"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="3"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="3"/>
+      <c r="B38" s="12"/>
+      <c r="C38" s="12"/>
+      <c r="D38" s="13"/>
+      <c r="E38" s="14"/>
+      <c r="F38" s="13"/>
+      <c r="G38" s="13"/>
+      <c r="H38" s="14"/>
     </row>
     <row r="39" spans="1:8" ht="39.950000000000003" customHeight="1">
-      <c r="A39" s="6">
+      <c r="A39" s="11">
         <v>36</v>
       </c>
-      <c r="B39" s="10"/>
-      <c r="C39" s="10"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="3"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
-      <c r="H39" s="3"/>
+      <c r="B39" s="12"/>
+      <c r="C39" s="12"/>
+      <c r="D39" s="13"/>
+      <c r="E39" s="14"/>
+      <c r="F39" s="13"/>
+      <c r="G39" s="13"/>
+      <c r="H39" s="14"/>
     </row>
     <row r="40" spans="1:8" ht="39.950000000000003" customHeight="1">
-      <c r="A40" s="6">
+      <c r="A40" s="11">
         <v>37</v>
       </c>
-      <c r="B40" s="10"/>
-      <c r="C40" s="10"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="3"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
-      <c r="H40" s="3"/>
+      <c r="B40" s="12"/>
+      <c r="C40" s="12"/>
+      <c r="D40" s="13"/>
+      <c r="E40" s="14"/>
+      <c r="F40" s="13"/>
+      <c r="G40" s="13"/>
+      <c r="H40" s="14"/>
     </row>
     <row r="41" spans="1:8" ht="39.950000000000003" customHeight="1">
-      <c r="A41" s="6">
+      <c r="A41" s="11">
         <v>38</v>
       </c>
-      <c r="B41" s="10"/>
-      <c r="C41" s="10"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="3"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="14"/>
-      <c r="H41" s="3"/>
+      <c r="B41" s="12"/>
+      <c r="C41" s="12"/>
+      <c r="D41" s="13"/>
+      <c r="E41" s="14"/>
+      <c r="F41" s="13"/>
+      <c r="G41" s="13"/>
+      <c r="H41" s="14"/>
     </row>
     <row r="42" spans="1:8" ht="39.950000000000003" customHeight="1">
-      <c r="A42" s="6">
+      <c r="A42" s="11">
         <v>39</v>
       </c>
-      <c r="B42" s="10"/>
-      <c r="C42" s="10"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="3"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="14"/>
-      <c r="H42" s="3"/>
+      <c r="B42" s="12"/>
+      <c r="C42" s="12"/>
+      <c r="D42" s="13"/>
+      <c r="E42" s="14"/>
+      <c r="F42" s="13"/>
+      <c r="G42" s="13"/>
+      <c r="H42" s="14"/>
     </row>
     <row r="43" spans="1:8" ht="39.950000000000003" customHeight="1">
-      <c r="A43" s="6">
+      <c r="A43" s="11">
         <v>40</v>
       </c>
-      <c r="B43" s="10"/>
-      <c r="C43" s="10"/>
-      <c r="D43" s="14"/>
-      <c r="E43" s="3"/>
-      <c r="F43" s="14"/>
-      <c r="G43" s="14"/>
-      <c r="H43" s="3"/>
+      <c r="B43" s="12"/>
+      <c r="C43" s="12"/>
+      <c r="D43" s="13"/>
+      <c r="E43" s="14"/>
+      <c r="F43" s="13"/>
+      <c r="G43" s="13"/>
+      <c r="H43" s="14"/>
     </row>
     <row r="44" spans="1:8" ht="39.950000000000003" customHeight="1">
-      <c r="A44" s="6">
+      <c r="A44" s="11">
         <v>41</v>
       </c>
-      <c r="B44" s="10"/>
-      <c r="C44" s="10"/>
-      <c r="D44" s="14"/>
-      <c r="E44" s="3"/>
-      <c r="F44" s="14"/>
-      <c r="G44" s="14"/>
-      <c r="H44" s="3"/>
+      <c r="B44" s="12"/>
+      <c r="C44" s="12"/>
+      <c r="D44" s="13"/>
+      <c r="E44" s="14"/>
+      <c r="F44" s="13"/>
+      <c r="G44" s="13"/>
+      <c r="H44" s="14"/>
     </row>
     <row r="45" spans="1:8" ht="39.950000000000003" customHeight="1">
-      <c r="A45" s="6">
+      <c r="A45" s="11">
         <v>42</v>
       </c>
-      <c r="B45" s="10"/>
-      <c r="C45" s="10"/>
-      <c r="D45" s="14"/>
-      <c r="E45" s="3"/>
-      <c r="F45" s="14"/>
-      <c r="G45" s="14"/>
-      <c r="H45" s="3"/>
+      <c r="B45" s="12"/>
+      <c r="C45" s="12"/>
+      <c r="D45" s="13"/>
+      <c r="E45" s="14"/>
+      <c r="F45" s="13"/>
+      <c r="G45" s="13"/>
+      <c r="H45" s="14"/>
     </row>
     <row r="46" spans="1:8" ht="39.950000000000003" customHeight="1">
-      <c r="A46" s="6">
+      <c r="A46" s="11">
         <v>43</v>
       </c>
-      <c r="B46" s="10"/>
-      <c r="C46" s="10"/>
-      <c r="D46" s="14"/>
-      <c r="E46" s="3"/>
-      <c r="F46" s="14"/>
-      <c r="G46" s="14"/>
-      <c r="H46" s="3"/>
+      <c r="B46" s="12"/>
+      <c r="C46" s="12"/>
+      <c r="D46" s="13"/>
+      <c r="E46" s="14"/>
+      <c r="F46" s="13"/>
+      <c r="G46" s="13"/>
+      <c r="H46" s="14"/>
     </row>
     <row r="47" spans="1:8" ht="39.950000000000003" customHeight="1">
-      <c r="A47" s="6">
+      <c r="A47" s="11">
         <v>44</v>
       </c>
-      <c r="B47" s="10"/>
-      <c r="C47" s="10"/>
-      <c r="D47" s="14"/>
-      <c r="E47" s="3"/>
-      <c r="F47" s="14"/>
-      <c r="G47" s="14"/>
-      <c r="H47" s="3"/>
+      <c r="B47" s="12"/>
+      <c r="C47" s="12"/>
+      <c r="D47" s="13"/>
+      <c r="E47" s="14"/>
+      <c r="F47" s="13"/>
+      <c r="G47" s="13"/>
+      <c r="H47" s="14"/>
     </row>
     <row r="48" spans="1:8" ht="39.950000000000003" customHeight="1">
-      <c r="A48" s="6">
+      <c r="A48" s="11">
         <v>45</v>
       </c>
-      <c r="B48" s="10"/>
-      <c r="C48" s="10"/>
-      <c r="D48" s="14"/>
-      <c r="E48" s="3"/>
-      <c r="F48" s="14"/>
-      <c r="G48" s="14"/>
-      <c r="H48" s="3"/>
+      <c r="B48" s="12"/>
+      <c r="C48" s="12"/>
+      <c r="D48" s="13"/>
+      <c r="E48" s="14"/>
+      <c r="F48" s="13"/>
+      <c r="G48" s="13"/>
+      <c r="H48" s="14"/>
     </row>
     <row r="49" spans="1:8" ht="39.950000000000003" customHeight="1">
-      <c r="A49" s="6">
+      <c r="A49" s="11">
         <v>46</v>
       </c>
-      <c r="B49" s="10"/>
-      <c r="C49" s="10"/>
-      <c r="D49" s="14"/>
-      <c r="E49" s="3"/>
-      <c r="F49" s="14"/>
-      <c r="G49" s="14"/>
-      <c r="H49" s="3"/>
+      <c r="B49" s="12"/>
+      <c r="C49" s="12"/>
+      <c r="D49" s="13"/>
+      <c r="E49" s="14"/>
+      <c r="F49" s="13"/>
+      <c r="G49" s="13"/>
+      <c r="H49" s="14"/>
     </row>
     <row r="50" spans="1:8" ht="39.950000000000003" customHeight="1">
-      <c r="A50" s="6">
+      <c r="A50" s="11">
         <v>47</v>
       </c>
-      <c r="B50" s="10"/>
-      <c r="C50" s="10"/>
-      <c r="D50" s="14"/>
-      <c r="E50" s="3"/>
-      <c r="F50" s="14"/>
-      <c r="G50" s="14"/>
-      <c r="H50" s="3"/>
+      <c r="B50" s="12"/>
+      <c r="C50" s="12"/>
+      <c r="D50" s="13"/>
+      <c r="E50" s="14"/>
+      <c r="F50" s="13"/>
+      <c r="G50" s="13"/>
+      <c r="H50" s="14"/>
     </row>
     <row r="51" spans="1:8" ht="39.950000000000003" customHeight="1">
-      <c r="A51" s="6">
+      <c r="A51" s="11">
         <v>48</v>
       </c>
-      <c r="B51" s="10"/>
-      <c r="C51" s="10"/>
-      <c r="D51" s="14"/>
-      <c r="E51" s="3"/>
-      <c r="F51" s="14"/>
-      <c r="G51" s="14"/>
-      <c r="H51" s="3"/>
+      <c r="B51" s="12"/>
+      <c r="C51" s="12"/>
+      <c r="D51" s="13"/>
+      <c r="E51" s="14"/>
+      <c r="F51" s="13"/>
+      <c r="G51" s="13"/>
+      <c r="H51" s="14"/>
     </row>
     <row r="52" spans="1:8" ht="39.950000000000003" customHeight="1">
-      <c r="A52" s="6">
+      <c r="A52" s="11">
         <v>49</v>
       </c>
-      <c r="B52" s="10"/>
-      <c r="C52" s="10"/>
-      <c r="D52" s="14"/>
-      <c r="E52" s="3"/>
-      <c r="F52" s="14"/>
-      <c r="G52" s="14"/>
-      <c r="H52" s="3"/>
+      <c r="B52" s="12"/>
+      <c r="C52" s="12"/>
+      <c r="D52" s="13"/>
+      <c r="E52" s="14"/>
+      <c r="F52" s="13"/>
+      <c r="G52" s="13"/>
+      <c r="H52" s="14"/>
     </row>
     <row r="53" spans="1:8" ht="39.950000000000003" customHeight="1">
-      <c r="A53" s="6">
+      <c r="A53" s="11">
         <v>50</v>
       </c>
-      <c r="B53" s="10"/>
-      <c r="C53" s="10"/>
-      <c r="D53" s="14"/>
-      <c r="E53" s="3"/>
-      <c r="F53" s="14"/>
-      <c r="G53" s="14"/>
-      <c r="H53" s="3"/>
+      <c r="B53" s="12"/>
+      <c r="C53" s="12"/>
+      <c r="D53" s="13"/>
+      <c r="E53" s="14"/>
+      <c r="F53" s="13"/>
+      <c r="G53" s="13"/>
+      <c r="H53" s="14"/>
     </row>
     <row r="54" spans="1:8" ht="39.950000000000003" customHeight="1">
-      <c r="A54" s="6">
+      <c r="A54" s="11">
         <v>51</v>
       </c>
-      <c r="B54" s="10"/>
-      <c r="C54" s="10"/>
-      <c r="D54" s="14"/>
-      <c r="E54" s="3"/>
-      <c r="F54" s="14"/>
-      <c r="G54" s="14"/>
-      <c r="H54" s="3"/>
+      <c r="B54" s="12"/>
+      <c r="C54" s="12"/>
+      <c r="D54" s="13"/>
+      <c r="E54" s="14"/>
+      <c r="F54" s="13"/>
+      <c r="G54" s="13"/>
+      <c r="H54" s="14"/>
     </row>
     <row r="55" spans="1:8" ht="39.950000000000003" customHeight="1">
-      <c r="A55" s="6">
+      <c r="A55" s="11">
         <v>52</v>
       </c>
-      <c r="B55" s="10"/>
-      <c r="C55" s="10"/>
-      <c r="D55" s="14"/>
-      <c r="E55" s="3"/>
-      <c r="F55" s="14"/>
-      <c r="G55" s="14"/>
-      <c r="H55" s="3"/>
+      <c r="B55" s="12"/>
+      <c r="C55" s="12"/>
+      <c r="D55" s="13"/>
+      <c r="E55" s="14"/>
+      <c r="F55" s="13"/>
+      <c r="G55" s="13"/>
+      <c r="H55" s="14"/>
     </row>
     <row r="56" spans="1:8" ht="39.950000000000003" customHeight="1">
-      <c r="A56" s="6">
+      <c r="A56" s="11">
         <v>53</v>
       </c>
-      <c r="B56" s="10"/>
-      <c r="C56" s="10"/>
-      <c r="D56" s="14"/>
-      <c r="E56" s="3"/>
-      <c r="F56" s="14"/>
-      <c r="G56" s="14"/>
-      <c r="H56" s="3"/>
+      <c r="B56" s="12"/>
+      <c r="C56" s="12"/>
+      <c r="D56" s="13"/>
+      <c r="E56" s="14"/>
+      <c r="F56" s="13"/>
+      <c r="G56" s="13"/>
+      <c r="H56" s="14"/>
     </row>
     <row r="57" spans="1:8" ht="39.950000000000003" customHeight="1">
-      <c r="A57" s="6">
+      <c r="A57" s="11">
         <v>54</v>
       </c>
-      <c r="B57" s="10"/>
-      <c r="C57" s="10"/>
-      <c r="D57" s="14"/>
-      <c r="E57" s="3"/>
-      <c r="F57" s="14"/>
-      <c r="G57" s="14"/>
-      <c r="H57" s="3"/>
+      <c r="B57" s="12"/>
+      <c r="C57" s="12"/>
+      <c r="D57" s="13"/>
+      <c r="E57" s="14"/>
+      <c r="F57" s="13"/>
+      <c r="G57" s="13"/>
+      <c r="H57" s="14"/>
     </row>
     <row r="58" spans="1:8" ht="39.950000000000003" customHeight="1">
-      <c r="A58" s="6">
+      <c r="A58" s="11">
         <v>55</v>
       </c>
-      <c r="B58" s="10"/>
-      <c r="C58" s="10"/>
-      <c r="D58" s="14"/>
-      <c r="E58" s="3"/>
-      <c r="F58" s="14"/>
-      <c r="G58" s="14"/>
-      <c r="H58" s="3"/>
+      <c r="B58" s="12"/>
+      <c r="C58" s="12"/>
+      <c r="D58" s="13"/>
+      <c r="E58" s="14"/>
+      <c r="F58" s="13"/>
+      <c r="G58" s="13"/>
+      <c r="H58" s="14"/>
     </row>
     <row r="59" spans="1:8" ht="39.950000000000003" customHeight="1">
-      <c r="A59" s="6">
+      <c r="A59" s="11">
         <v>56</v>
       </c>
-      <c r="B59" s="10"/>
-      <c r="C59" s="10"/>
-      <c r="D59" s="14"/>
-      <c r="E59" s="3"/>
-      <c r="F59" s="14"/>
-      <c r="G59" s="14"/>
-      <c r="H59" s="3"/>
+      <c r="B59" s="12"/>
+      <c r="C59" s="12"/>
+      <c r="D59" s="13"/>
+      <c r="E59" s="14"/>
+      <c r="F59" s="13"/>
+      <c r="G59" s="13"/>
+      <c r="H59" s="14"/>
     </row>
     <row r="60" spans="1:8" ht="39.950000000000003" customHeight="1">
-      <c r="A60" s="6">
+      <c r="A60" s="11">
         <v>57</v>
       </c>
-      <c r="B60" s="10"/>
-      <c r="C60" s="10"/>
-      <c r="D60" s="14"/>
-      <c r="E60" s="3"/>
-      <c r="F60" s="14"/>
-      <c r="G60" s="14"/>
-      <c r="H60" s="3"/>
+      <c r="B60" s="12"/>
+      <c r="C60" s="12"/>
+      <c r="D60" s="13"/>
+      <c r="E60" s="14"/>
+      <c r="F60" s="13"/>
+      <c r="G60" s="13"/>
+      <c r="H60" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/Excel/liste_groupe_2.xlsx
+++ b/Excel/liste_groupe_2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\AppData\Roaming\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39817F75-F6F1-41E4-A1E9-76907E448FC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1473849A-1167-4B19-99C0-BD67794A3541}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8685" yWindow="5535" windowWidth="20115" windowHeight="9945" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="91">
   <si>
     <t>Période de présence aux cours 2025 - 2026 (01/11/2025)</t>
   </si>
@@ -77,9 +77,6 @@
   </si>
   <si>
     <t>Saladin</t>
-  </si>
-  <si>
-    <t>31/12/1899</t>
   </si>
   <si>
     <t>N/A</t>
@@ -873,16 +870,16 @@
         <v>17</v>
       </c>
       <c r="D5" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F5" s="10" t="s">
+      <c r="G5" s="10" t="s">
         <v>20</v>
-      </c>
-      <c r="G5" s="10" t="s">
-        <v>21</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>15</v>
@@ -893,22 +890,22 @@
         <v>3</v>
       </c>
       <c r="B6" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="D6" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="E6" s="2" t="s">
         <v>24</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>25</v>
       </c>
       <c r="F6" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>15</v>
@@ -919,22 +916,22 @@
         <v>4</v>
       </c>
       <c r="B7" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="D7" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="E7" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G7" s="10" t="s">
         <v>30</v>
-      </c>
-      <c r="F7" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="G7" s="10" t="s">
-        <v>31</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>15</v>
@@ -945,22 +942,22 @@
         <v>5</v>
       </c>
       <c r="B8" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="D8" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="E8" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>35</v>
       </c>
       <c r="F8" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>15</v>
@@ -971,22 +968,22 @@
         <v>6</v>
       </c>
       <c r="B9" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="D9" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D9" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G9" s="10" t="s">
         <v>39</v>
-      </c>
-      <c r="F9" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="G9" s="10" t="s">
-        <v>40</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>15</v>
@@ -997,22 +994,22 @@
         <v>7</v>
       </c>
       <c r="B10" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C10" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="D10" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="E10" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G10" s="10" t="s">
         <v>43</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="F10" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="G10" s="10" t="s">
-        <v>44</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>15</v>
@@ -1023,22 +1020,22 @@
         <v>8</v>
       </c>
       <c r="B11" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="D11" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="D11" s="10" t="s">
-        <v>47</v>
-      </c>
       <c r="E11" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F11" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>15</v>
@@ -1049,22 +1046,22 @@
         <v>9</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C12" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D12" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="D12" s="10" t="s">
-        <v>50</v>
-      </c>
       <c r="E12" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F12" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>15</v>
@@ -1075,22 +1072,22 @@
         <v>10</v>
       </c>
       <c r="B13" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C13" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="D13" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="D13" s="10" t="s">
-        <v>54</v>
-      </c>
       <c r="E13" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F13" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>15</v>
@@ -1101,22 +1098,22 @@
         <v>11</v>
       </c>
       <c r="B14" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C14" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="D14" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="D14" s="10" t="s">
+      <c r="E14" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E14" s="2" t="s">
-        <v>59</v>
-      </c>
       <c r="F14" s="10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>15</v>
@@ -1127,22 +1124,22 @@
         <v>12</v>
       </c>
       <c r="B15" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="C15" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="D15" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="D15" s="10" t="s">
+      <c r="E15" s="2" t="s">
         <v>62</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>63</v>
       </c>
       <c r="F15" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>15</v>
@@ -1153,22 +1150,22 @@
         <v>13</v>
       </c>
       <c r="B16" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C16" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="D16" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="D16" s="10" t="s">
+      <c r="E16" s="2" t="s">
         <v>67</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>68</v>
       </c>
       <c r="F16" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>15</v>
@@ -1179,22 +1176,22 @@
         <v>14</v>
       </c>
       <c r="B17" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C17" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="D17" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="D17" s="10" t="s">
+      <c r="E17" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="E17" s="2" t="s">
-        <v>73</v>
-      </c>
       <c r="F17" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G17" s="10" t="s">
         <v>20</v>
-      </c>
-      <c r="G17" s="10" t="s">
-        <v>21</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>15</v>
@@ -1205,13 +1202,13 @@
         <v>15</v>
       </c>
       <c r="B18" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C18" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="D18" s="10" t="s">
         <v>75</v>
-      </c>
-      <c r="D18" s="10" t="s">
-        <v>76</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>12</v>
@@ -1220,7 +1217,7 @@
         <v>13</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>15</v>
@@ -1231,22 +1228,22 @@
         <v>16</v>
       </c>
       <c r="B19" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="C19" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="D19" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="D19" s="10" t="s">
-        <v>80</v>
-      </c>
       <c r="E19" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>15</v>
@@ -1257,22 +1254,22 @@
         <v>17</v>
       </c>
       <c r="B20" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="C20" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="C20" s="8" t="s">
+      <c r="D20" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="D20" s="10" t="s">
-        <v>83</v>
-      </c>
       <c r="E20" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F20" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G20" s="10" t="s">
         <v>39</v>
-      </c>
-      <c r="F20" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="G20" s="10" t="s">
-        <v>40</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>15</v>
@@ -1283,22 +1280,22 @@
         <v>18</v>
       </c>
       <c r="B21" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C21" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="D21" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="D21" s="10" t="s">
+      <c r="E21" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F21" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G21" s="10" t="s">
         <v>86</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="F21" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="G21" s="10" t="s">
-        <v>87</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>15</v>
@@ -1309,22 +1306,22 @@
         <v>19</v>
       </c>
       <c r="B22" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="C22" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="C22" s="8" t="s">
+      <c r="D22" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="D22" s="10" t="s">
+      <c r="E22" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F22" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G22" s="10" t="s">
         <v>90</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="F22" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="G22" s="10" t="s">
-        <v>91</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>15</v>

--- a/Excel/liste_groupe_2.xlsx
+++ b/Excel/liste_groupe_2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\AppData\Roaming\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1473849A-1167-4B19-99C0-BD67794A3541}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C72B7F9-538A-4C3E-AFE4-D8531BF019A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="59">
   <si>
     <t>Période de présence aux cours 2025 - 2026 (01/11/2025)</t>
   </si>
@@ -58,7 +58,7 @@
     <t>Seida</t>
   </si>
   <si>
-    <t>01/01/1983</t>
+    <t/>
   </si>
   <si>
     <t>Soudan</t>
@@ -67,12 +67,6 @@
     <t>F</t>
   </si>
   <si>
-    <t>10/09/2024</t>
-  </si>
-  <si>
-    <t>01/01/1900</t>
-  </si>
-  <si>
     <t>ABDRAMAN IBRAHIM</t>
   </si>
   <si>
@@ -85,54 +79,33 @@
     <t>M</t>
   </si>
   <si>
-    <t>01/09/2025</t>
-  </si>
-  <si>
     <t>ABIA</t>
   </si>
   <si>
     <t>Flore</t>
   </si>
   <si>
-    <t>19/08/2000</t>
-  </si>
-  <si>
     <t>République démocratique du Congo</t>
   </si>
   <si>
-    <t>23/09/2025</t>
-  </si>
-  <si>
     <t>AVAGYAN</t>
   </si>
   <si>
     <t>Karen</t>
   </si>
   <si>
-    <t>04/10/1980</t>
-  </si>
-  <si>
     <t>Arménie</t>
   </si>
   <si>
-    <t>10/12/2024</t>
-  </si>
-  <si>
     <t>BURDULI</t>
   </si>
   <si>
     <t>Sopio</t>
   </si>
   <si>
-    <t>02/04/1997</t>
-  </si>
-  <si>
     <t>Géorgie</t>
   </si>
   <si>
-    <t>11/10/2023</t>
-  </si>
-  <si>
     <t>HIRPA</t>
   </si>
   <si>
@@ -142,63 +115,33 @@
     <t>Éthiopie</t>
   </si>
   <si>
-    <t>16/09/2025</t>
-  </si>
-  <si>
     <t>JISHKARIANI</t>
   </si>
   <si>
     <t>Nino</t>
   </si>
   <si>
-    <t>11/02/1980</t>
-  </si>
-  <si>
-    <t>06/11/2025</t>
-  </si>
-  <si>
     <t>KATCHATRYAN</t>
   </si>
   <si>
     <t>Anna</t>
   </si>
   <si>
-    <t>20/05/1980</t>
-  </si>
-  <si>
-    <t>07/11/2025</t>
-  </si>
-  <si>
     <t>Mariam</t>
   </si>
   <si>
-    <t>26/08/1986</t>
-  </si>
-  <si>
-    <t>06/10/2022</t>
-  </si>
-  <si>
     <t>MUGENI</t>
   </si>
   <si>
     <t>Chantal</t>
   </si>
   <si>
-    <t>31/12/1996</t>
-  </si>
-  <si>
-    <t>25/09/2025</t>
-  </si>
-  <si>
     <t>MUSTAFAYEV</t>
   </si>
   <si>
     <t>Elshan</t>
   </si>
   <si>
-    <t>17/07/1978</t>
-  </si>
-  <si>
     <t>Azerbaïdjan</t>
   </si>
   <si>
@@ -208,39 +151,24 @@
     <t>Wuod</t>
   </si>
   <si>
-    <t>01/06/1970</t>
-  </si>
-  <si>
     <t>Irak</t>
   </si>
   <si>
-    <t>15/11/2022</t>
-  </si>
-  <si>
     <t>PETUKHOVA</t>
   </si>
   <si>
     <t>Mariila</t>
   </si>
   <si>
-    <t>05/11/1951</t>
-  </si>
-  <si>
     <t>Ukraine</t>
   </si>
   <si>
-    <t>10/09/2025</t>
-  </si>
-  <si>
     <t>RAHHAL</t>
   </si>
   <si>
     <t>Abdelkader</t>
   </si>
   <si>
-    <t>03/07/1984</t>
-  </si>
-  <si>
     <t>Algérie</t>
   </si>
   <si>
@@ -250,52 +178,28 @@
     <t>Kajol</t>
   </si>
   <si>
-    <t>08/07/2004</t>
-  </si>
-  <si>
-    <t>03/09/2025</t>
-  </si>
-  <si>
     <t>SHOTSHA</t>
   </si>
   <si>
     <t>M'wemwe</t>
   </si>
   <si>
-    <t>05/05/1981</t>
-  </si>
-  <si>
     <t>TOLA</t>
   </si>
   <si>
     <t>Boja</t>
   </si>
   <si>
-    <t>27/08/2004</t>
-  </si>
-  <si>
     <t>TSAGAREISHVILI</t>
   </si>
   <si>
     <t>Gela</t>
   </si>
   <si>
-    <t>05/11/1984</t>
-  </si>
-  <si>
-    <t>28/05/2024</t>
-  </si>
-  <si>
     <t>WRETA</t>
   </si>
   <si>
     <t>Abeje</t>
-  </si>
-  <si>
-    <t>05/05/1997</t>
-  </si>
-  <si>
-    <t>11/09/2025</t>
   </si>
 </sst>
 </file>
@@ -853,10 +757,10 @@
         <v>13</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -864,25 +768,25 @@
         <v>2</v>
       </c>
       <c r="B5" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="F5" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F5" s="10" t="s">
-        <v>19</v>
-      </c>
       <c r="G5" s="10" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -890,25 +794,25 @@
         <v>3</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F6" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -916,25 +820,25 @@
         <v>4</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -942,25 +846,25 @@
         <v>5</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="F8" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -968,25 +872,25 @@
         <v>6</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -994,25 +898,25 @@
         <v>7</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1020,25 +924,25 @@
         <v>8</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F11" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>47</v>
+        <v>11</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1046,25 +950,25 @@
         <v>9</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>49</v>
+        <v>11</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F12" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1072,25 +976,25 @@
         <v>10</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>53</v>
+        <v>11</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F13" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>54</v>
+        <v>11</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1098,25 +1002,25 @@
         <v>11</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>57</v>
+        <v>11</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="F14" s="10" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1124,25 +1028,25 @@
         <v>12</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>61</v>
+        <v>11</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="F15" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>63</v>
+        <v>11</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1150,25 +1054,25 @@
         <v>13</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>66</v>
+        <v>11</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="F16" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1176,25 +1080,25 @@
         <v>14</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>71</v>
+        <v>11</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1202,13 +1106,13 @@
         <v>15</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>75</v>
+        <v>11</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>12</v>
@@ -1217,10 +1121,10 @@
         <v>13</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>76</v>
+        <v>11</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1228,25 +1132,25 @@
         <v>16</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>77</v>
+        <v>51</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>78</v>
+        <v>52</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1254,25 +1158,25 @@
         <v>17</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>80</v>
+        <v>53</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>81</v>
+        <v>54</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>82</v>
+        <v>11</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="F20" s="10" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1280,25 +1184,25 @@
         <v>18</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>83</v>
+        <v>55</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>84</v>
+        <v>56</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>85</v>
+        <v>11</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>86</v>
+        <v>11</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1306,25 +1210,25 @@
         <v>19</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>87</v>
+        <v>57</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>88</v>
+        <v>58</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>89</v>
+        <v>11</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>90</v>
+        <v>11</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="39.950000000000003" customHeight="1">

--- a/Excel/liste_groupe_2.xlsx
+++ b/Excel/liste_groupe_2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\AppData\Roaming\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C72B7F9-538A-4C3E-AFE4-D8531BF019A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A322FC1E-A0CA-4819-8EFA-5456A6C1B612}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Excel/liste_groupe_2.xlsx
+++ b/Excel/liste_groupe_2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\AppData\Roaming\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A322FC1E-A0CA-4819-8EFA-5456A6C1B612}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FD1E095-10CE-42D9-B139-2ED3A7D60810}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="91">
   <si>
     <t>Période de présence aux cours 2025 - 2026 (01/11/2025)</t>
   </si>
@@ -58,7 +58,7 @@
     <t>Seida</t>
   </si>
   <si>
-    <t/>
+    <t>01/01/1983</t>
   </si>
   <si>
     <t>Soudan</t>
@@ -67,6 +67,12 @@
     <t>F</t>
   </si>
   <si>
+    <t>10/09/2024</t>
+  </si>
+  <si>
+    <t>01/01/1900</t>
+  </si>
+  <si>
     <t>ABDRAMAN IBRAHIM</t>
   </si>
   <si>
@@ -79,33 +85,54 @@
     <t>M</t>
   </si>
   <si>
+    <t>01/09/2025</t>
+  </si>
+  <si>
     <t>ABIA</t>
   </si>
   <si>
     <t>Flore</t>
   </si>
   <si>
+    <t>19/08/2000</t>
+  </si>
+  <si>
     <t>République démocratique du Congo</t>
   </si>
   <si>
+    <t>23/09/2025</t>
+  </si>
+  <si>
     <t>AVAGYAN</t>
   </si>
   <si>
     <t>Karen</t>
   </si>
   <si>
+    <t>04/10/1980</t>
+  </si>
+  <si>
     <t>Arménie</t>
   </si>
   <si>
+    <t>10/12/2024</t>
+  </si>
+  <si>
     <t>BURDULI</t>
   </si>
   <si>
     <t>Sopio</t>
   </si>
   <si>
+    <t>02/04/1997</t>
+  </si>
+  <si>
     <t>Géorgie</t>
   </si>
   <si>
+    <t>11/10/2023</t>
+  </si>
+  <si>
     <t>HIRPA</t>
   </si>
   <si>
@@ -115,33 +142,63 @@
     <t>Éthiopie</t>
   </si>
   <si>
+    <t>16/09/2025</t>
+  </si>
+  <si>
     <t>JISHKARIANI</t>
   </si>
   <si>
     <t>Nino</t>
   </si>
   <si>
+    <t>11/02/1980</t>
+  </si>
+  <si>
+    <t>06/11/2025</t>
+  </si>
+  <si>
     <t>KATCHATRYAN</t>
   </si>
   <si>
     <t>Anna</t>
   </si>
   <si>
+    <t>20/05/1980</t>
+  </si>
+  <si>
+    <t>07/11/2025</t>
+  </si>
+  <si>
     <t>Mariam</t>
   </si>
   <si>
+    <t>26/08/1986</t>
+  </si>
+  <si>
+    <t>06/10/2022</t>
+  </si>
+  <si>
     <t>MUGENI</t>
   </si>
   <si>
     <t>Chantal</t>
   </si>
   <si>
+    <t>31/12/1996</t>
+  </si>
+  <si>
+    <t>25/09/2025</t>
+  </si>
+  <si>
     <t>MUSTAFAYEV</t>
   </si>
   <si>
     <t>Elshan</t>
   </si>
   <si>
+    <t>17/07/1978</t>
+  </si>
+  <si>
     <t>Azerbaïdjan</t>
   </si>
   <si>
@@ -151,24 +208,39 @@
     <t>Wuod</t>
   </si>
   <si>
+    <t>01/06/1970</t>
+  </si>
+  <si>
     <t>Irak</t>
   </si>
   <si>
+    <t>15/11/2022</t>
+  </si>
+  <si>
     <t>PETUKHOVA</t>
   </si>
   <si>
     <t>Mariila</t>
   </si>
   <si>
+    <t>05/11/1951</t>
+  </si>
+  <si>
     <t>Ukraine</t>
   </si>
   <si>
+    <t>10/09/2025</t>
+  </si>
+  <si>
     <t>RAHHAL</t>
   </si>
   <si>
     <t>Abdelkader</t>
   </si>
   <si>
+    <t>03/07/1984</t>
+  </si>
+  <si>
     <t>Algérie</t>
   </si>
   <si>
@@ -178,28 +250,52 @@
     <t>Kajol</t>
   </si>
   <si>
+    <t>08/07/2004</t>
+  </si>
+  <si>
+    <t>03/09/2025</t>
+  </si>
+  <si>
     <t>SHOTSHA</t>
   </si>
   <si>
     <t>M'wemwe</t>
   </si>
   <si>
+    <t>05/05/1981</t>
+  </si>
+  <si>
     <t>TOLA</t>
   </si>
   <si>
     <t>Boja</t>
   </si>
   <si>
+    <t>27/08/2004</t>
+  </si>
+  <si>
     <t>TSAGAREISHVILI</t>
   </si>
   <si>
     <t>Gela</t>
   </si>
   <si>
+    <t>05/11/1984</t>
+  </si>
+  <si>
+    <t>28/05/2024</t>
+  </si>
+  <si>
     <t>WRETA</t>
   </si>
   <si>
     <t>Abeje</t>
+  </si>
+  <si>
+    <t>05/05/1997</t>
+  </si>
+  <si>
+    <t>11/09/2025</t>
   </si>
 </sst>
 </file>
@@ -757,10 +853,10 @@
         <v>13</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -768,25 +864,25 @@
         <v>2</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -794,25 +890,25 @@
         <v>3</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F6" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -820,25 +916,25 @@
         <v>4</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -846,25 +942,25 @@
         <v>5</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F8" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -872,25 +968,25 @@
         <v>6</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -898,25 +994,25 @@
         <v>7</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>11</v>
+        <v>43</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -924,25 +1020,25 @@
         <v>8</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F11" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -950,25 +1046,25 @@
         <v>9</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F12" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -976,25 +1072,25 @@
         <v>10</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>11</v>
+        <v>53</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F13" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>11</v>
+        <v>54</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1002,25 +1098,25 @@
         <v>11</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>11</v>
+        <v>57</v>
       </c>
       <c r="E14" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F14" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G14" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="F14" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="G14" s="10" t="s">
-        <v>11</v>
-      </c>
       <c r="H14" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1028,25 +1124,25 @@
         <v>12</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>11</v>
+        <v>61</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="F15" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>11</v>
+        <v>63</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1054,25 +1150,25 @@
         <v>13</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>11</v>
+        <v>66</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="F16" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>11</v>
+        <v>68</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1080,25 +1176,25 @@
         <v>14</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>11</v>
+        <v>71</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1106,13 +1202,13 @@
         <v>15</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>11</v>
+        <v>75</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>12</v>
@@ -1121,10 +1217,10 @@
         <v>13</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>11</v>
+        <v>76</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1132,25 +1228,25 @@
         <v>16</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>11</v>
+        <v>79</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1158,25 +1254,25 @@
         <v>17</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>53</v>
+        <v>80</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>54</v>
+        <v>81</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>11</v>
+        <v>82</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="F20" s="10" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1184,25 +1280,25 @@
         <v>18</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>55</v>
+        <v>83</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>56</v>
+        <v>84</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>11</v>
+        <v>85</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>11</v>
+        <v>86</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1210,25 +1306,25 @@
         <v>19</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>57</v>
+        <v>87</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>58</v>
+        <v>88</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>11</v>
+        <v>89</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>11</v>
+        <v>90</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="39.950000000000003" customHeight="1">
